--- a/策划/excel/17_Item.xlsx
+++ b/策划/excel/17_Item.xlsx
@@ -1404,8 +1404,10 @@
       <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
-        <v>21</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[{"id":"item-stone","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E6" t="s">
         <v>22</v>
@@ -1427,8 +1429,10 @@
       <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
-        <v>26</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170002-1","type":210001,"target":"ENEMY","params":{"amount":4,"hits":2,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170002-2","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E7" t="s">
         <v>22</v>
@@ -1450,8 +1454,10 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
-        <v>29</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170003-1","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170003-2","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E8" t="s">
         <v>22</v>
@@ -1473,8 +1479,10 @@
       <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
-        <v>32</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170004-1","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170004-2","type":210015,"target":"SELF","params":{"stat":200002,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E9" t="s">
         <v>33</v>
@@ -1496,8 +1504,10 @@
       <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" t="s">
-        <v>37</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170005-1","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170005-2","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E10" t="s">
         <v>22</v>
@@ -1519,8 +1529,10 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-      <c r="D11" t="s">
-        <v>40</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170006-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":2,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170006-2","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E11" t="s">
         <v>22</v>
@@ -1542,8 +1554,10 @@
       <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="D12" t="s">
-        <v>43</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170007-1","type":210001,"target":"ENEMY","params":{"amount":4,"hits":3,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170007-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E12" t="s">
         <v>22</v>
@@ -1565,8 +1579,10 @@
       <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="D13" t="s">
-        <v>46</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170008-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170008-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E13" t="s">
         <v>22</v>
@@ -1588,8 +1604,10 @@
       <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="D14" t="s">
-        <v>49</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170009-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170009-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E14" t="s">
         <v>22</v>
@@ -1611,8 +1629,10 @@
       <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="D15" t="s">
-        <v>52</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170010-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":3,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170010-2","type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170010-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170010-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E15" t="s">
         <v>22</v>
@@ -1634,8 +1654,10 @@
       <c r="C16" t="s">
         <v>54</v>
       </c>
-      <c r="D16" t="s">
-        <v>55</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170011-1","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170011-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E16" t="s">
         <v>22</v>
@@ -1657,8 +1679,10 @@
       <c r="C17" t="s">
         <v>57</v>
       </c>
-      <c r="D17" t="s">
-        <v>58</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170012-1","type":210002,"target":"SELF","params":{"amount":14,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170012-2","type":210015,"target":"SELF","params":{"stat":200002,"amount":3,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170012-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170012-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E17" t="s">
         <v>33</v>
@@ -1680,8 +1704,10 @@
       <c r="C18" t="s">
         <v>60</v>
       </c>
-      <c r="D18" t="s">
-        <v>61</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170013-1","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170013-2","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E18" t="s">
         <v>22</v>
@@ -1703,8 +1729,10 @@
       <c r="C19" t="s">
         <v>63</v>
       </c>
-      <c r="D19" t="s">
-        <v>64</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170014-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170014-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E19" t="s">
         <v>22</v>
@@ -1726,8 +1754,10 @@
       <c r="C20" t="s">
         <v>66</v>
       </c>
-      <c r="D20" t="s">
-        <v>67</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170015-1","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170015-2","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E20" t="s">
         <v>22</v>
@@ -1749,8 +1779,10 @@
       <c r="C21" t="s">
         <v>69</v>
       </c>
-      <c r="D21" t="s">
-        <v>70</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170016-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170016-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E21" t="s">
         <v>22</v>
@@ -1772,8 +1804,10 @@
       <c r="C22" t="s">
         <v>72</v>
       </c>
-      <c r="D22" t="s">
-        <v>73</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170017-1","type":210001,"target":"ENEMY","params":{"amount":3,"hits":3,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E22" t="s">
         <v>22</v>
@@ -1795,8 +1829,10 @@
       <c r="C23" t="s">
         <v>75</v>
       </c>
-      <c r="D23" t="s">
-        <v>76</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170018-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170018-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E23" t="s">
         <v>22</v>
@@ -1818,8 +1854,10 @@
       <c r="C24" t="s">
         <v>78</v>
       </c>
-      <c r="D24" t="s">
-        <v>79</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170019-1","type":210031,"target":"SELF","params":{"amount":15},"children":[],"elseEffects":[]},{"id":"item-170019-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E24" t="s">
         <v>33</v>
@@ -1841,8 +1879,10 @@
       <c r="C25" t="s">
         <v>82</v>
       </c>
-      <c r="D25" t="s">
-        <v>83</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170020-1","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170020-2","type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E25" t="s">
         <v>22</v>
@@ -1864,8 +1904,10 @@
       <c r="C26" t="s">
         <v>85</v>
       </c>
-      <c r="D26" t="s">
-        <v>86</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170021-1","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170021-2","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E26" t="s">
         <v>22</v>
@@ -1887,8 +1929,10 @@
       <c r="C27" t="s">
         <v>88</v>
       </c>
-      <c r="D27" t="s">
-        <v>89</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170022-1","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170022-2","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170022-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170022-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E27" t="s">
         <v>22</v>
@@ -1910,8 +1954,10 @@
       <c r="C28" t="s">
         <v>91</v>
       </c>
-      <c r="D28" t="s">
-        <v>92</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170023-1","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170023-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E28" t="s">
         <v>22</v>
@@ -1933,8 +1979,10 @@
       <c r="C29" t="s">
         <v>94</v>
       </c>
-      <c r="D29" t="s">
-        <v>95</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170024-1","type":210003,"target":"SELF","params":{"amount":5},"children":[],"elseEffects":[]},{"id":"item-170024-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E29" t="s">
         <v>33</v>
@@ -1956,8 +2004,10 @@
       <c r="C30" t="s">
         <v>97</v>
       </c>
-      <c r="D30" t="s">
-        <v>98</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170025-1","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170025-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E30" t="s">
         <v>22</v>
@@ -1979,8 +2029,10 @@
       <c r="C31" t="s">
         <v>100</v>
       </c>
-      <c r="D31" t="s">
-        <v>101</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170026-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170026-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E31" t="s">
         <v>22</v>
@@ -2002,8 +2054,10 @@
       <c r="C32" t="s">
         <v>103</v>
       </c>
-      <c r="D32" t="s">
-        <v>104</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170027-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170027-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E32" t="s">
         <v>22</v>
@@ -2025,8 +2079,10 @@
       <c r="C33" t="s">
         <v>106</v>
       </c>
-      <c r="D33" t="s">
-        <v>107</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170028-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170028-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E33" t="s">
         <v>22</v>
@@ -2048,8 +2104,10 @@
       <c r="C34" t="s">
         <v>109</v>
       </c>
-      <c r="D34" t="s">
-        <v>110</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170029-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170029-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E34" t="s">
         <v>22</v>
@@ -2071,8 +2129,10 @@
       <c r="C35" t="s">
         <v>112</v>
       </c>
-      <c r="D35" t="s">
-        <v>113</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170030-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170030-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E35" t="s">
         <v>22</v>
@@ -2094,8 +2154,10 @@
       <c r="C36" t="s">
         <v>115</v>
       </c>
-      <c r="D36" t="s">
-        <v>116</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170031-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170031-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E36" t="s">
         <v>22</v>
@@ -2117,8 +2179,10 @@
       <c r="C37" t="s">
         <v>118</v>
       </c>
-      <c r="D37" t="s">
-        <v>119</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170032-1","type":210001,"target":"ENEMY","params":{"amount":11,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170032-2","type":210003,"target":"SELF","params":{"amount":8},"children":[],"elseEffects":[]},{"id":"item-170032-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170032-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E37" t="s">
         <v>22</v>
@@ -2140,8 +2204,10 @@
       <c r="C38" t="s">
         <v>121</v>
       </c>
-      <c r="D38" t="s">
-        <v>122</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170033-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170033-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E38" t="s">
         <v>22</v>
@@ -2163,8 +2229,10 @@
       <c r="C39" t="s">
         <v>124</v>
       </c>
-      <c r="D39" t="s">
-        <v>125</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170034-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170034-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E39" t="s">
         <v>22</v>
@@ -2186,8 +2254,10 @@
       <c r="C40" t="s">
         <v>127</v>
       </c>
-      <c r="D40" t="s">
-        <v>128</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170035-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170035-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E40" t="s">
         <v>22</v>
@@ -2209,8 +2279,10 @@
       <c r="C41" t="s">
         <v>130</v>
       </c>
-      <c r="D41" t="s">
-        <v>131</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170036-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":2,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170036-2","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E41" t="s">
         <v>22</v>
@@ -2232,8 +2304,10 @@
       <c r="C42" t="s">
         <v>133</v>
       </c>
-      <c r="D42" t="s">
-        <v>134</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170037-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170037-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E42" t="s">
         <v>22</v>
@@ -2255,8 +2329,10 @@
       <c r="C43" t="s">
         <v>136</v>
       </c>
-      <c r="D43" t="s">
-        <v>137</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170038-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170038-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E43" t="s">
         <v>22</v>
@@ -2278,8 +2354,10 @@
       <c r="C44" t="s">
         <v>139</v>
       </c>
-      <c r="D44" t="s">
-        <v>140</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170039-1","type":210003,"target":"SELF","params":{"amount":5},"children":[],"elseEffects":[]},{"id":"item-170039-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E44" t="s">
         <v>33</v>
@@ -2301,8 +2379,10 @@
       <c r="C45" t="s">
         <v>142</v>
       </c>
-      <c r="D45" t="s">
-        <v>143</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170040-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170040-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E45" t="s">
         <v>22</v>
@@ -2324,8 +2404,10 @@
       <c r="C46" t="s">
         <v>145</v>
       </c>
-      <c r="D46" t="s">
-        <v>146</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170041-1","type":210003,"target":"SELF","params":{"amount":5},"children":[],"elseEffects":[]},{"id":"item-170041-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E46" t="s">
         <v>33</v>
@@ -2347,8 +2429,10 @@
       <c r="C47" t="s">
         <v>148</v>
       </c>
-      <c r="D47" t="s">
-        <v>149</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170042-1","type":210001,"target":"ENEMY","params":{"amount":11,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170042-2","type":210003,"target":"SELF","params":{"amount":8},"children":[],"elseEffects":[]},{"id":"item-170042-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170042-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E47" t="s">
         <v>22</v>
@@ -2370,8 +2454,10 @@
       <c r="C48" t="s">
         <v>151</v>
       </c>
-      <c r="D48" t="s">
-        <v>152</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170043-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170043-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E48" t="s">
         <v>22</v>
@@ -2393,8 +2479,10 @@
       <c r="C49" t="s">
         <v>154</v>
       </c>
-      <c r="D49" t="s">
-        <v>155</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170044-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170044-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E49" t="s">
         <v>22</v>
@@ -2416,8 +2504,10 @@
       <c r="C50" t="s">
         <v>157</v>
       </c>
-      <c r="D50" t="s">
-        <v>158</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170045-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170045-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E50" t="s">
         <v>22</v>
@@ -2439,8 +2529,10 @@
       <c r="C51" t="s">
         <v>160</v>
       </c>
-      <c r="D51" t="s">
-        <v>161</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170046-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170046-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E51" t="s">
         <v>22</v>
@@ -2462,8 +2554,10 @@
       <c r="C52" t="s">
         <v>163</v>
       </c>
-      <c r="D52" t="s">
-        <v>164</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170047-1","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170047-2","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E52" t="s">
         <v>22</v>
@@ -2485,8 +2579,10 @@
       <c r="C53" t="s">
         <v>166</v>
       </c>
-      <c r="D53" t="s">
-        <v>167</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170048-1","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170048-2","type":210015,"target":"SELF","params":{"stat":200002,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -2508,8 +2604,10 @@
       <c r="C54" t="s">
         <v>169</v>
       </c>
-      <c r="D54" t="s">
-        <v>170</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170049-1","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170049-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E54" t="s">
         <v>22</v>
@@ -2531,8 +2629,10 @@
       <c r="C55" t="s">
         <v>172</v>
       </c>
-      <c r="D55" t="s">
-        <v>173</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170050-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170050-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E55" t="s">
         <v>22</v>
@@ -2554,8 +2654,10 @@
       <c r="C56" t="s">
         <v>175</v>
       </c>
-      <c r="D56" t="s">
-        <v>176</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170051-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170051-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E56" t="s">
         <v>22</v>
@@ -2577,8 +2679,10 @@
       <c r="C57" t="s">
         <v>178</v>
       </c>
-      <c r="D57" t="s">
-        <v>179</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170052-1","type":210001,"target":"ENEMY","params":{"amount":11,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170052-2","type":210003,"target":"SELF","params":{"amount":8},"children":[],"elseEffects":[]},{"id":"item-170052-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170052-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E57" t="s">
         <v>22</v>
@@ -2600,8 +2704,10 @@
       <c r="C58" t="s">
         <v>181</v>
       </c>
-      <c r="D58" t="s">
-        <v>182</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170053-1","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170053-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E58" t="s">
         <v>22</v>
@@ -2623,8 +2729,10 @@
       <c r="C59" t="s">
         <v>184</v>
       </c>
-      <c r="D59" t="s">
-        <v>185</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170054-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170054-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E59" t="s">
         <v>22</v>
@@ -2646,8 +2754,10 @@
       <c r="C60" t="s">
         <v>187</v>
       </c>
-      <c r="D60" t="s">
-        <v>188</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170055-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170055-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E60" t="s">
         <v>22</v>
@@ -2669,8 +2779,10 @@
       <c r="C61" t="s">
         <v>190</v>
       </c>
-      <c r="D61" t="s">
-        <v>191</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170056-1","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170056-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E61" t="s">
         <v>22</v>
@@ -2692,8 +2804,10 @@
       <c r="C62" t="s">
         <v>193</v>
       </c>
-      <c r="D62" t="s">
-        <v>194</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170057-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170057-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E62" t="s">
         <v>22</v>
@@ -2715,8 +2829,10 @@
       <c r="C63" t="s">
         <v>196</v>
       </c>
-      <c r="D63" t="s">
-        <v>197</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170058-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170058-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E63" t="s">
         <v>22</v>
@@ -2738,8 +2854,10 @@
       <c r="C64" t="s">
         <v>199</v>
       </c>
-      <c r="D64" t="s">
-        <v>200</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170059-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":3,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170059-2","type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170059-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170059-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E64" t="s">
         <v>22</v>
@@ -2761,8 +2879,10 @@
       <c r="C65" t="s">
         <v>202</v>
       </c>
-      <c r="D65" t="s">
-        <v>203</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170060-1","type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E65" t="s">
         <v>22</v>
@@ -2784,8 +2904,10 @@
       <c r="C66" t="s">
         <v>205</v>
       </c>
-      <c r="D66" t="s">
-        <v>206</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170061-1","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170061-2","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E66" t="s">
         <v>22</v>
@@ -2807,8 +2929,10 @@
       <c r="C67" t="s">
         <v>208</v>
       </c>
-      <c r="D67" t="s">
-        <v>209</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170062-1","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170062-2","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170062-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170062-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E67" t="s">
         <v>22</v>
@@ -2830,8 +2954,10 @@
       <c r="C68" t="s">
         <v>211</v>
       </c>
-      <c r="D68" t="s">
-        <v>212</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170063-1","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":4,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170063-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E68" t="s">
         <v>22</v>
@@ -2853,8 +2979,10 @@
       <c r="C69" t="s">
         <v>214</v>
       </c>
-      <c r="D69" t="s">
-        <v>215</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170064-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170064-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E69" t="s">
         <v>22</v>
@@ -2876,8 +3004,10 @@
       <c r="C70" t="s">
         <v>217</v>
       </c>
-      <c r="D70" t="s">
-        <v>218</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170065-1","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170065-2","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E70" t="s">
         <v>22</v>
@@ -2899,8 +3029,10 @@
       <c r="C71" t="s">
         <v>220</v>
       </c>
-      <c r="D71" t="s">
-        <v>221</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170066-1","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170066-2","type":210015,"target":"SELF","params":{"stat":200002,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -2922,8 +3054,10 @@
       <c r="C72" t="s">
         <v>223</v>
       </c>
-      <c r="D72" t="s">
-        <v>224</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170067-1","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170067-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E72" t="s">
         <v>22</v>
@@ -2945,8 +3079,10 @@
       <c r="C73" t="s">
         <v>226</v>
       </c>
-      <c r="D73" t="s">
-        <v>227</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170068-1","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170068-2","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E73" t="s">
         <v>22</v>
@@ -2968,8 +3104,10 @@
       <c r="C74" t="s">
         <v>229</v>
       </c>
-      <c r="D74" t="s">
-        <v>230</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170069-1","type":210002,"target":"SELF","params":{"amount":11,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170069-2","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E74" t="s">
         <v>22</v>
@@ -2991,8 +3129,10 @@
       <c r="C75" t="s">
         <v>232</v>
       </c>
-      <c r="D75" t="s">
-        <v>233</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170070-1","type":210031,"target":"SELF","params":{"amount":15},"children":[],"elseEffects":[]},{"id":"item-170070-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -3014,8 +3154,10 @@
       <c r="C76" t="s">
         <v>235</v>
       </c>
-      <c r="D76" t="s">
-        <v>236</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170071-1","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170071-2","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E76" t="s">
         <v>22</v>
@@ -3037,8 +3179,10 @@
       <c r="C77" t="s">
         <v>238</v>
       </c>
-      <c r="D77" t="s">
-        <v>239</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170072-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":3,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170072-2","type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170072-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170072-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E77" t="s">
         <v>22</v>
@@ -3060,8 +3204,10 @@
       <c r="C78" t="s">
         <v>241</v>
       </c>
-      <c r="D78" t="s">
-        <v>242</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170073-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170073-2","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E78" t="s">
         <v>22</v>
@@ -3083,8 +3229,10 @@
       <c r="C79" t="s">
         <v>244</v>
       </c>
-      <c r="D79" t="s">
-        <v>245</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170074-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170074-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E79" t="s">
         <v>22</v>
@@ -3106,8 +3254,10 @@
       <c r="C80" t="s">
         <v>247</v>
       </c>
-      <c r="D80" t="s">
-        <v>248</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170075-1","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170075-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E80" t="s">
         <v>22</v>
@@ -3129,8 +3279,10 @@
       <c r="C81" t="s">
         <v>250</v>
       </c>
-      <c r="D81" t="s">
-        <v>251</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170076-1","type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170076-2","type":210003,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E81" t="s">
         <v>22</v>
@@ -3152,8 +3304,10 @@
       <c r="C82" t="s">
         <v>253</v>
       </c>
-      <c r="D82" t="s">
-        <v>254</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170077-1","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170077-2","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E82" t="s">
         <v>22</v>
@@ -3175,8 +3329,10 @@
       <c r="C83" t="s">
         <v>256</v>
       </c>
-      <c r="D83" t="s">
-        <v>257</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170078-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":2,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170078-2","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E83" t="s">
         <v>22</v>
@@ -3198,8 +3354,10 @@
       <c r="C84" t="s">
         <v>259</v>
       </c>
-      <c r="D84" t="s">
-        <v>260</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170079-1","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170079-2","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E84" t="s">
         <v>22</v>
@@ -3221,8 +3379,10 @@
       <c r="C85" t="s">
         <v>262</v>
       </c>
-      <c r="D85" t="s">
-        <v>263</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170080-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170080-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E85" t="s">
         <v>22</v>
@@ -3244,8 +3404,10 @@
       <c r="C86" t="s">
         <v>265</v>
       </c>
-      <c r="D86" t="s">
-        <v>266</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170081-1","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170081-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E86" t="s">
         <v>22</v>
@@ -3267,8 +3429,10 @@
       <c r="C87" t="s">
         <v>268</v>
       </c>
-      <c r="D87" t="s">
-        <v>269</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170082-1","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170082-2","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170082-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170082-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E87" t="s">
         <v>22</v>
@@ -3290,8 +3454,10 @@
       <c r="C88" t="s">
         <v>271</v>
       </c>
-      <c r="D88" t="s">
-        <v>272</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170083-1","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170083-2","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E88" t="s">
         <v>22</v>
@@ -3313,8 +3479,10 @@
       <c r="C89" t="s">
         <v>274</v>
       </c>
-      <c r="D89" t="s">
-        <v>275</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170084-1","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170084-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E89" t="s">
         <v>22</v>
@@ -3336,8 +3504,10 @@
       <c r="C90" t="s">
         <v>277</v>
       </c>
-      <c r="D90" t="s">
-        <v>278</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170085-1","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170085-2","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E90" t="s">
         <v>22</v>
@@ -3359,8 +3529,10 @@
       <c r="C91" t="s">
         <v>280</v>
       </c>
-      <c r="D91" t="s">
-        <v>281</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170086-1","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170086-2","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E91" t="s">
         <v>22</v>
@@ -3382,8 +3554,10 @@
       <c r="C92" t="s">
         <v>283</v>
       </c>
-      <c r="D92" t="s">
-        <v>284</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170087-1","type":210001,"target":"ENEMY","params":{"amount":4,"hits":4,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170087-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E92" t="s">
         <v>22</v>
@@ -3405,8 +3579,10 @@
       <c r="C93" t="s">
         <v>286</v>
       </c>
-      <c r="D93" t="s">
-        <v>287</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170088-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170088-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E93" t="s">
         <v>22</v>
@@ -3428,8 +3604,10 @@
       <c r="C94" t="s">
         <v>289</v>
       </c>
-      <c r="D94" t="s">
-        <v>290</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170089-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170089-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E94" t="s">
         <v>22</v>
@@ -3451,8 +3629,10 @@
       <c r="C95" t="s">
         <v>292</v>
       </c>
-      <c r="D95" t="s">
-        <v>293</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170090-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170090-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E95" t="s">
         <v>22</v>
@@ -3474,8 +3654,10 @@
       <c r="C96" t="s">
         <v>295</v>
       </c>
-      <c r="D96" t="s">
-        <v>296</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170091-1","type":210031,"target":"SELF","params":{"amount":15},"children":[],"elseEffects":[]},{"id":"item-170091-2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E96" t="s">
         <v>33</v>
@@ -3497,8 +3679,10 @@
       <c r="C97" t="s">
         <v>298</v>
       </c>
-      <c r="D97" t="s">
-        <v>299</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170092-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170092-2","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170092-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170092-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E97" t="s">
         <v>22</v>
@@ -3520,8 +3704,10 @@
       <c r="C98" t="s">
         <v>301</v>
       </c>
-      <c r="D98" t="s">
-        <v>302</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170093-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":3,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170093-2","type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170093-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170093-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E98" t="s">
         <v>22</v>
@@ -3543,8 +3729,10 @@
       <c r="C99" t="s">
         <v>304</v>
       </c>
-      <c r="D99" t="s">
-        <v>305</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170094-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170094-2","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170094-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170094-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E99" t="s">
         <v>22</v>
@@ -3566,8 +3754,10 @@
       <c r="C100" t="s">
         <v>307</v>
       </c>
-      <c r="D100" t="s">
-        <v>308</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170095-1","type":210010,"target":"ENEMY","params":{"status":200005,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170095-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E100" t="s">
         <v>22</v>
@@ -3589,8 +3779,10 @@
       <c r="C101" t="s">
         <v>310</v>
       </c>
-      <c r="D101" t="s">
-        <v>311</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170096-1","type":210001,"target":"ENEMY","params":{"amount":11,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170096-2","type":210003,"target":"SELF","params":{"amount":8},"children":[],"elseEffects":[]},{"id":"item-170096-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170096-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E101" t="s">
         <v>22</v>
@@ -3612,8 +3804,10 @@
       <c r="C102" t="s">
         <v>313</v>
       </c>
-      <c r="D102" t="s">
-        <v>314</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170097-1","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":4,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170097-2","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E102" t="s">
         <v>22</v>
@@ -3635,8 +3829,10 @@
       <c r="C103" t="s">
         <v>316</v>
       </c>
-      <c r="D103" t="s">
-        <v>317</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170098-1","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"item-170098-2","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E103" t="s">
         <v>22</v>
@@ -3658,8 +3854,10 @@
       <c r="C104" t="s">
         <v>319</v>
       </c>
-      <c r="D104" t="s">
-        <v>320</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170099-1","type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170099-2","type":210003,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E104" t="s">
         <v>22</v>
@@ -3681,8 +3879,10 @@
       <c r="C105" t="s">
         <v>322</v>
       </c>
-      <c r="D105" t="s">
-        <v>323</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170100-1","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170100-2","type":210003,"target":"SELF","params":{"amount":4},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E105" t="s">
         <v>22</v>
@@ -3704,8 +3904,10 @@
       <c r="C106" t="s">
         <v>325</v>
       </c>
-      <c r="D106" t="s">
-        <v>326</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170101-1","type":210002,"target":"SELF","params":{"amount":11,"scale":true},"children":[],"elseEffects":[]},{"id":"item-170101-2","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E106" t="s">
         <v>22</v>
@@ -3727,8 +3929,10 @@
       <c r="C107" t="s">
         <v>328</v>
       </c>
-      <c r="D107" t="s">
-        <v>329</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>[{"id":"item-170102-1","type":210015,"target":"SELF","params":{"stat":200001,"amount":3,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"item-170102-2","type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"item-170102-delayed","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"item-170102-block","type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="E107" t="s">
         <v>22</v>
